--- a/laporan_padel_dki_jakarta_2026-10-22.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-22.xlsx
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.175.000</t>
+          <t>Rp9.370.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.425.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.460.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp10.500.000</t>
+          <t>Rp10.600.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.370.000</t>
+          <t>Rp2.710.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.480.000</t>
+          <t>Rp4.978.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp2.085.000</t>
+          <t>Rp2.184.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3489,16 +3489,16 @@
         <v>68</v>
       </c>
       <c r="D99" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp398.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp778.000</t>
+          <t>Rp1.478.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.699.000</t>
+          <t>Rp2.899.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.750.000</t>
+          <t>Rp8.850.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp2.843.000</t>
+          <t>Rp3.043.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp8.000.000</t>
+          <t>Rp7.750.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.375.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp760.000</t>
+          <t>Rp1.060.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp50.400.000</t>
+          <t>Rp51.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.908.000</t>
+          <t>Rp7.096.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.580.000</t>
+          <t>Rp6.367.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.860.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp10.675.000</t>
+          <t>Rp10.825.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp21.775.000</t>
+          <t>Rp22.200.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.435.000</t>
+          <t>Rp5.145.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp17.540.000</t>
+          <t>Rp18.340.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp3.050.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.930.000</t>
+          <t>Rp3.215.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.090.000</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.890.000</t>
+          <t>Rp4.225.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9459,16 +9459,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.194.000</t>
+          <t>Rp1.592.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-22.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-22.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.760.000</t>
+          <t>Rp1.880.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.384.000</t>
+          <t>Rp3.984.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.370.000</t>
+          <t>Rp9.870.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.594.000</t>
+          <t>Rp11.006.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp896.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.355.000</t>
+          <t>Rp2.655.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.435.000</t>
+          <t>Rp14.935.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp1.825.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp688.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp891.000</t>
+          <t>Rp1.031.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.027.000</t>
+          <t>Rp3.267.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.720.000</t>
+          <t>Rp5.180.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp5.285.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.620.000</t>
+          <t>Rp1.470.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>72</v>
       </c>
       <c r="D44" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp5.770.000</t>
+          <t>Rp4.780.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>56</v>
       </c>
       <c r="D51" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.608.000</t>
+          <t>Rp5.184.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp792.000</t>
+          <t>Rp968.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp596.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp10.600.000</t>
+          <t>Rp10.820.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.108.000</t>
+          <t>Rp2.504.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.360.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp6.860.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp3.474.000</t>
+          <t>Rp3.573.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>80</v>
       </c>
       <c r="D88" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp1.493.000</t>
+          <t>Rp1.991.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>90</v>
       </c>
       <c r="D94" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp596.000</t>
+          <t>Rp695.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp1.192.000</t>
+          <t>Rp1.490.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp3.975.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3582,16 +3582,16 @@
         <v>36</v>
       </c>
       <c r="D102" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.539.000</t>
+          <t>Rp1.701.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3692,19 +3692,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.473.500</t>
+          <t>Rp12.188.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.385.000</t>
+          <t>Rp5.585.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.540.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.899.000</t>
+          <t>Rp2.199.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp8.850.000</t>
+          <t>Rp10.200.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.145.000</t>
+          <t>Rp1.755.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp10.900.000</t>
+          <t>Rp10.550.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp15.850.000</t>
+          <t>Rp18.800.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.625.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.564.000</t>
+          <t>Rp4.752.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp10.800.000</t>
+          <t>Rp11.600.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp6.237.000</t>
+          <t>Rp6.534.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp5.110.000</t>
+          <t>Rp4.690.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp1.990.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp51.400.000</t>
+          <t>Rp52.600.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp4.925.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp3.780.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.030.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.345.000</t>
+          <t>Rp4.570.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp12.960.000</t>
+          <t>Rp11.460.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.065.000</t>
+          <t>Rp10.290.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp566.000</t>
+          <t>Rp635.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp7.096.000</t>
+          <t>Rp7.654.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.445.000</t>
+          <t>Rp5.845.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.025.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.381.000</t>
+          <t>Rp2.088.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.367.000</t>
+          <t>Rp6.704.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp8.250.000</t>
+          <t>Rp8.400.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.200.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.603.000</t>
+          <t>Rp5.051.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.375.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.985.000</t>
+          <t>Rp5.430.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp6.845.000</t>
+          <t>Rp5.130.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp10.825.000</t>
+          <t>Rp12.300.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.564.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp1.339.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.775.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp5.130.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8137,16 +8137,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.505.000</t>
+          <t>Rp3.510.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.124.990</t>
+          <t>Rp2.449.994</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp3.925.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.285.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp1.508.000</t>
+          <t>Rp1.707.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.574.994</t>
+          <t>Rp3.699.994</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.215.000</t>
+          <t>Rp3.860.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp980.000</t>
+          <t>Rp1.570.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9459,16 +9459,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.592.000</t>
+          <t>Rp1.911.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-22.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-22.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.384.000</t>
+          <t>Rp2.583.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp15.860.000</t>
+          <t>Rp16.460.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.984.000</t>
+          <t>Rp4.284.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp974.000</t>
+          <t>Rp1.109.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>67</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.431.986</t>
+          <t>Rp6.178.985</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.006.500</t>
+          <t>Rp11.144.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.760.000</t>
+          <t>Rp3.536.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.655.000</t>
+          <t>Rp3.495.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp13.021.000</t>
+          <t>Rp14.017.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp3.675.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.825.000</t>
+          <t>Rp2.225.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.031.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp5.180.000</t>
+          <t>Rp4.720.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.285.000</t>
+          <t>Rp4.905.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.560.000</t>
+          <t>Rp5.060.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.470.000</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.170.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.184.000</t>
+          <t>Rp5.472.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>30</v>
       </c>
       <c r="D53" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp990.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp968.000</t>
+          <t>Rp1.056.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>36</v>
       </c>
       <c r="D55" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp175.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp596.000</t>
+          <t>Rp745.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.142.000</t>
+          <t>Rp2.170.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp10.820.000</t>
+          <t>Rp10.220.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.710.000</t>
+          <t>Rp3.280.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp1.020.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>41</v>
       </c>
       <c r="D68" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.978.000</t>
+          <t>Rp5.277.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>108</v>
       </c>
       <c r="D71" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp5.552.500</t>
+          <t>Rp6.252.500</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp695.000</t>
+          <t>Rp1.035.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>90</v>
       </c>
       <c r="D74" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp4.875.000</t>
+          <t>Rp5.525.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp6.860.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.575.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp3.573.000</t>
+          <t>Rp3.772.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp2.184.000</t>
+          <t>Rp2.482.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>90</v>
       </c>
       <c r="D90" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp2.802.800</t>
+          <t>Rp3.203.200</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>36</v>
       </c>
       <c r="D92" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>90</v>
       </c>
       <c r="D94" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp695.000</t>
+          <t>Rp924.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp2.095.000</t>
+          <t>Rp2.595.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3582,16 +3582,16 @@
         <v>36</v>
       </c>
       <c r="D102" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.701.000</t>
+          <t>Rp1.539.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.478.000</t>
+          <t>Rp2.256.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.400.000</t>
+          <t>Rp7.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.180.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.380.000</t>
+          <t>Rp7.985.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.815.000</t>
+          <t>Rp5.165.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.199.000</t>
+          <t>Rp2.299.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp178.000</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp18.800.000</t>
+          <t>Rp19.650.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.440.000</t>
+          <t>Rp2.570.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp555.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp850.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.325.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.752.000</t>
+          <t>Rp4.356.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp8.700.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp230.000</t>
+          <t>Rp682.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp10.400.000</t>
+          <t>Rp11.400.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp11.600.000</t>
+          <t>Rp13.200.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp6.534.000</t>
+          <t>Rp7.722.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.690.000</t>
+          <t>Rp5.070.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp6.580.000</t>
+          <t>Rp6.930.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5803,16 +5803,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp5.920.000</t>
+          <t>Rp5.535.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5834,16 +5834,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp11.550.000</t>
+          <t>Rp11.900.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5865,16 +5865,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp10.550.000</t>
+          <t>Rp11.500.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp520.000</t>
+          <t>Rp840.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp19.690.000</t>
+          <t>Rp23.760.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.925.000</t>
+          <t>Rp5.275.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.030.000</t>
+          <t>Rp3.474.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp10.855.000</t>
+          <t>Rp11.190.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.525.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp6.010.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.460.000</t>
+          <t>Rp11.790.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp635.000</t>
+          <t>Rp903.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.350.000</t>
+          <t>Rp13.850.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.476.000</t>
+          <t>Rp9.162.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp17.542.000</t>
+          <t>Rp18.382.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp3.322.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.088.000</t>
+          <t>Rp3.164.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.188.000</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.300.000</t>
+          <t>Rp21.900.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp10.950.000</t>
+          <t>Rp12.000.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rp81.000 - Rp175.000</t>
+          <t>Rp10.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7300,16 +7300,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp680.000</t>
+          <t>Rp940.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp1.275.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>85</v>
       </c>
       <c r="D30" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.270.000</t>
+          <t>Rp3.710.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp5.051.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp12.300.000</t>
+          <t>Rp12.975.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp6.564.000</t>
+          <t>Rp6.852.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.339.000</t>
+          <t>Rp769.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.340.000</t>
+          <t>Rp1.628.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp22.200.000</t>
+          <t>Rp22.900.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.775.000</t>
+          <t>Rp2.775.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp9.205.000</t>
+          <t>Rp9.480.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp28.400.000</t>
+          <t>Rp29.600.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8137,16 +8137,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp505.000</t>
+          <t>Rp690.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp8.090.000</t>
+          <t>Rp9.010.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.840.000</t>
+          <t>Rp6.190.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.890.000</t>
+          <t>Rp3.488.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.345.000</t>
+          <t>Rp5.115.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.449.994</t>
+          <t>Rp3.249.990</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp792.000</t>
+          <t>Rp990.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp18.340.000</t>
+          <t>Rp18.820.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.285.000</t>
+          <t>Rp4.845.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.699.994</t>
+          <t>Rp4.024.993</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.360.000</t>
+          <t>Rp3.930.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.860.000</t>
+          <t>Rp4.755.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.570.000</t>
+          <t>Rp2.480.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.783.000</t>
+          <t>Rp1.981.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.225.000</t>
+          <t>Rp3.975.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>90</v>
       </c>
       <c r="D40" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.675.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-22.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-22.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.880.000</t>
+          <t>Rp1.960.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp4.975.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.536.000</t>
+          <t>Rp3.824.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.495.000</t>
+          <t>Rp3.075.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.935.000</t>
+          <t>Rp15.180.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>15</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp688.000</t>
+          <t>Rp1.064.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.060.000</t>
+          <t>Rp5.310.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>72</v>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp4.780.000</t>
+          <t>Rp6.215.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp1.056.000</t>
+          <t>Rp1.144.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.775.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>90</v>
       </c>
       <c r="D74" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp5.525.000</t>
+          <t>Rp6.175.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>45</v>
       </c>
       <c r="D77" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>36</v>
       </c>
       <c r="D92" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.539.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.080.000</t>
+          <t>Rp3.180.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.586.000</t>
+          <t>Rp4.237.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp682.000</t>
+          <t>Rp744.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.250.000</t>
+          <t>Rp7.950.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.990.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.780.000</t>
+          <t>Rp4.080.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.900.000</t>
+          <t>Rp22.100.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp8.400.000</t>
+          <t>Rp7.890.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>80</v>
       </c>
       <c r="D29" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.475.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>85</v>
       </c>
       <c r="D30" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.710.000</t>
+          <t>Rp3.930.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp12.975.000</t>
+          <t>Rp13.050.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.775.000</t>
+          <t>Rp2.525.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp690.000</t>
+          <t>Rp1.060.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.115.000</t>
+          <t>Rp4.845.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.845.000</t>
+          <t>Rp4.455.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>120</v>
       </c>
       <c r="D35" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp6.430.000</t>
+          <t>Rp6.829.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.975.000</t>
+          <t>Rp4.525.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9459,16 +9459,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.911.000</t>
+          <t>Rp2.110.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -9490,16 +9490,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-22.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-22.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.178.985</t>
+          <t>Rp6.076.985</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.144.000</t>
+          <t>Rp11.222.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.720.000</t>
+          <t>Rp4.880.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>108</v>
       </c>
       <c r="D71" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp6.252.500</t>
+          <t>Rp6.552.500</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.035.000</t>
+          <t>Rp1.185.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.575.000</t>
+          <t>Rp2.725.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp8.275.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp19.650.000</t>
+          <t>Rp19.300.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp11.400.000</t>
+          <t>Rp12.400.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp5.070.000</t>
+          <t>Rp5.220.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.474.000</t>
+          <t>Rp3.593.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp903.000</t>
+          <t>Rp1.041.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.375.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.322.000</t>
+          <t>Rp3.518.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.100.000</t>
+          <t>Rp22.500.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.704.000</t>
+          <t>Rp7.190.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp7.890.000</t>
+          <t>Rp7.740.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.375.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp13.050.000</t>
+          <t>Rp13.300.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.130.000</t>
+          <t>Rp5.430.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8137,16 +8137,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.075.000</t>
+          <t>Rp6.225.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.981.000</t>
+          <t>Rp2.080.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>90</v>
       </c>
       <c r="D40" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp4.675.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
